--- a/reports/集团总公司_利润表_2026-05.xlsx
+++ b/reports/集团总公司_利润表_2026-05.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>232684908</v>
+        <v>253513710</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>177337977</v>
+        <v>192479050</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>798264946</v>
+        <v>868236114</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>723101</v>
+        <v>931273</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3355647</v>
+        <v>4348068</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>625208</v>
+        <v>813883</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2909380</v>
+        <v>3802381</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>529446</v>
+        <v>686670</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2466749</v>
+        <v>3207573</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>488860</v>
+        <v>633969</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2270660</v>
+        <v>2958641</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>265569</v>
+        <v>349021</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1233258</v>
+        <v>1626141</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>211712</v>
+        <v>275361</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>986270</v>
+        <v>1280653</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>229841012</v>
+        <v>249823533</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>174494081</v>
+        <v>188788873</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89643090</v>
+        <v>98268806</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>392154257</v>
+        <v>430830788</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1642249</v>
+        <v>2927956</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7646215</v>
+        <v>13567225</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1486890</v>
+        <v>2130157</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6910885</v>
+        <v>9872084</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79943203</v>
+        <v>84133398</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>370087846</v>
+        <v>390465170</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1692076</v>
+        <v>2125070</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>7886169</v>
+        <v>9886763</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>741143</v>
+        <v>1060428</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3454122</v>
+        <v>4942720</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2663687</v>
+        <v>3174594</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>12346272</v>
+        <v>14828686</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1167888</v>
+        <v>1586597</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5425395</v>
+        <v>7409903</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>55170248</v>
+        <v>55255124</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>257789195</v>
+        <v>257637456</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>176683</v>
+        <v>174470</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>865348</v>
+        <v>875036</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3361430</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>15675142</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2243636</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>10444320</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>173669587</v>
+        <v>196413946</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>135047005</v>
+        <v>142794725</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>106440766</v>
+        <v>113907753</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>494061848</v>
+        <v>527841862</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28606239</v>
+        <v>28886972</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>133544588</v>
+        <v>133863944</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5646351</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>26144934</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1806400</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>8372566</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1127946</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>5236170</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1351556</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>6286021</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1011906</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4715114</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>673452</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3142824</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>560438</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2617802</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3120978</v>
+        <v>3116922</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14555783</v>
+        <v>14554973</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1478376</v>
+        <v>1467255</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6862139</v>
+        <v>6860981</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3826498</v>
+        <v>3815226</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>17753042</v>
+        <v>17728504</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>30139334</v>
+        <v>30317511</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>120392718</v>
+        <v>120332772</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>366631</v>
+        <v>3035631</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1759991</v>
+        <v>14040212</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1169141</v>
+        <v>1155882</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5695498</v>
+        <v>5758989</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1205839</v>
+        <v>1104037</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>5882605</v>
+        <v>5503825</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>124756</v>
+        <v>124053</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>607044</v>
+        <v>617340</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>493376</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2455946</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>987790</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>4579173</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328472</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1639555</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>245981</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1230215</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>409250</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2050705</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1402734</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>6547244</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>217615</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1093098</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163096</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>819308</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>271831</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1364518</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190422</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>954492</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136198</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>681407</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>109142</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>544964</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>408725</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>56171425</v>
+        <v>56836634</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66751622</v>
+        <v>67015352</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>564641</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2615018</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136989</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>682771</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>218018</v>
+        <v>216876</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1063846</v>
+        <v>1082797</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>55953407</v>
+        <v>57184399</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7420057</v>
+        <v>7309754</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>35960931</v>
+        <v>36629969</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48533350</v>
+        <v>49874645</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48533350</v>
+        <v>49874645</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48533350</v>
+        <v>49874645</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48533350</v>
+        <v>49874645</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48533350</v>
+        <v>49874645</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
